--- a/drawings/安楽寺本堂_空調換気/24時間換気計算書.xlsx
+++ b/drawings/安楽寺本堂_空調換気/24時間換気計算書.xlsx
@@ -141,7 +141,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="32">
+  <cellXfs count="35">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -198,14 +198,29 @@
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
@@ -223,12 +238,6 @@
     </xf>
     <xf numFmtId="167" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -595,7 +604,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:I79"/>
+  <dimension ref="A1:I88"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -769,7 +778,7 @@
     <row r="14" ht="15" customHeight="1">
       <c r="A14" s="8" t="inlineStr">
         <is>
-          <t>第3種機械換気設備（排気機：天井埋込形換気扇 常時運転／給気：外気導入グリル）。</t>
+          <t>第3種機械換気設備（排気機：パイプ用ファン 外壁貫通・常時運転／給気：外気導入グリル）。</t>
         </is>
       </c>
     </row>
@@ -1465,7 +1474,7 @@
     <row r="42">
       <c r="A42" s="3" t="inlineStr">
         <is>
-          <t>4. 有効換気量 Ve（機械換気設備：排気機）</t>
+          <t>4. 有効換気量 Ve（機械換気設備：排気機 パイプ用ファン）</t>
         </is>
       </c>
     </row>
@@ -1487,12 +1496,12 @@
       </c>
       <c r="D43" s="9" t="inlineStr">
         <is>
-          <t>ダクト径</t>
+          <t>パイプ径</t>
         </is>
       </c>
       <c r="E43" s="9" t="inlineStr">
         <is>
-          <t>ダクト実長
+          <t>パイプ実長
 L (m)</t>
         </is>
       </c>
@@ -1540,22 +1549,21 @@
         </is>
       </c>
       <c r="E44" s="19" t="n">
-        <v>0.8</v>
+        <v>0.5</v>
       </c>
       <c r="F44" s="19" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G44" s="10">
         <f>ROUND(E44+F44*$C$48+$F$48,1)</f>
         <v/>
       </c>
-      <c r="H44" s="10">
-        <f>IF(G44&lt;=20.0,80.5,"要P-Q確認")</f>
-        <v/>
+      <c r="H44" s="20" t="n">
+        <v>80</v>
       </c>
       <c r="I44" s="11" t="inlineStr">
         <is>
-          <t>パナソニック FY-17C8（単相100V）</t>
+          <t>三菱電機 V-08PP8-BL（壁付（外壁貫通）・単相100V）</t>
         </is>
       </c>
     </row>
@@ -1579,22 +1587,21 @@
         </is>
       </c>
       <c r="E45" s="19" t="n">
-        <v>0.8</v>
+        <v>0.5</v>
       </c>
       <c r="F45" s="19" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G45" s="10">
         <f>ROUND(E45+F45*$C$48+$F$48,1)</f>
         <v/>
       </c>
-      <c r="H45" s="10">
-        <f>IF(G45&lt;=20.0,80.5,"要P-Q確認")</f>
-        <v/>
+      <c r="H45" s="20" t="n">
+        <v>80</v>
       </c>
       <c r="I45" s="11" t="inlineStr">
         <is>
-          <t>パナソニック FY-17C8（単相100V）</t>
+          <t>三菱電機 V-08PP8-BL（壁付（外壁貫通）・単相100V）</t>
         </is>
       </c>
     </row>
@@ -1618,22 +1625,21 @@
         </is>
       </c>
       <c r="E46" s="19" t="n">
-        <v>0.8</v>
+        <v>0.5</v>
       </c>
       <c r="F46" s="19" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G46" s="10">
         <f>ROUND(E46+F46*$C$48+$F$48,1)</f>
         <v/>
       </c>
-      <c r="H46" s="10">
-        <f>IF(G46&lt;=20.0,80.5,"要P-Q確認")</f>
-        <v/>
+      <c r="H46" s="20" t="n">
+        <v>80</v>
       </c>
       <c r="I46" s="11" t="inlineStr">
         <is>
-          <t>パナソニック FY-17C8（単相100V）</t>
+          <t>三菱電機 V-08PP8-BL（壁付（外壁貫通）・単相100V）</t>
         </is>
       </c>
     </row>
@@ -1659,508 +1665,708 @@
       <c r="I47" s="15" t="inlineStr"/>
     </row>
     <row r="48">
-      <c r="A48" s="20" t="inlineStr">
+      <c r="A48" s="21" t="inlineStr">
         <is>
           <t>直管相当長の算定</t>
         </is>
       </c>
-      <c r="C48" s="21" t="n">
+      <c r="C48" s="22" t="n">
         <v>1.5</v>
       </c>
-      <c r="D48" s="20" t="inlineStr">
+      <c r="D48" s="21" t="inlineStr">
         <is>
           <t>m／90°曲り1個</t>
         </is>
       </c>
-      <c r="F48" s="21" t="n">
+      <c r="F48" s="22" t="n">
         <v>10</v>
       </c>
-      <c r="G48" s="20" t="inlineStr">
-        <is>
-          <t>m／外壁フード（深型・防虫網付）</t>
-        </is>
-      </c>
-    </row>
-    <row r="49" ht="36" customHeight="1">
-      <c r="A49" s="18" t="inlineStr">
-        <is>
-          <t>※有効換気量はメーカー公表値（FY-17C8：静圧時 直管相当長20m で 80.5 m³/h、30m で 76 m³/h、開放時 95 m³/h、消費電力 7.6W）。直管相当長が20m以下であることを確認し、20m時の値を採用（安全側）。</t>
+      <c r="G48" s="21" t="inlineStr">
+        <is>
+          <t>m／屋外深形フード（防虫網付）</t>
+        </is>
+      </c>
+    </row>
+    <row r="50" ht="28" customHeight="1">
+      <c r="A50" s="23" t="inlineStr">
+        <is>
+          <t>有効換気量の算定（V-08PP8-BL P-Q線図 60Hz：送風機静圧と、パイプ抵抗曲線〔VU管φ100・10m〕を直管相当長 10.5m に比例換算した抵抗との交点）</t>
         </is>
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="3" t="inlineStr">
+      <c r="A51" s="24" t="inlineStr"/>
+      <c r="B51" s="24" t="inlineStr">
+        <is>
+          <t>風量 Q</t>
+        </is>
+      </c>
+      <c r="C51" s="25" t="n"/>
+      <c r="D51" s="24" t="inlineStr">
+        <is>
+          <t>送風機静圧</t>
+        </is>
+      </c>
+      <c r="E51" s="25" t="n"/>
+      <c r="F51" s="24" t="inlineStr">
+        <is>
+          <t>抵抗 L=10.5m</t>
+        </is>
+      </c>
+      <c r="G51" s="25" t="n"/>
+      <c r="H51" s="24" t="inlineStr">
+        <is>
+          <t>差</t>
+        </is>
+      </c>
+      <c r="I51" s="24" t="inlineStr"/>
+    </row>
+    <row r="52">
+      <c r="A52" s="26" t="inlineStr"/>
+      <c r="B52" s="26" t="inlineStr">
+        <is>
+          <t>60 m³/h</t>
+        </is>
+      </c>
+      <c r="C52" s="25" t="n"/>
+      <c r="D52" s="26" t="inlineStr">
+        <is>
+          <t>23.1 Pa</t>
+        </is>
+      </c>
+      <c r="E52" s="25" t="n"/>
+      <c r="F52" s="26" t="inlineStr">
+        <is>
+          <t>6.0 Pa</t>
+        </is>
+      </c>
+      <c r="G52" s="25" t="n"/>
+      <c r="H52" s="26" t="inlineStr">
+        <is>
+          <t>+17.1 Pa</t>
+        </is>
+      </c>
+      <c r="I52" s="27" t="inlineStr"/>
+    </row>
+    <row r="53">
+      <c r="A53" s="26" t="inlineStr"/>
+      <c r="B53" s="26" t="inlineStr">
+        <is>
+          <t>70 m³/h</t>
+        </is>
+      </c>
+      <c r="C53" s="25" t="n"/>
+      <c r="D53" s="26" t="inlineStr">
+        <is>
+          <t>17.9 Pa</t>
+        </is>
+      </c>
+      <c r="E53" s="25" t="n"/>
+      <c r="F53" s="26" t="inlineStr">
+        <is>
+          <t>7.8 Pa</t>
+        </is>
+      </c>
+      <c r="G53" s="25" t="n"/>
+      <c r="H53" s="26" t="inlineStr">
+        <is>
+          <t>+10.1 Pa</t>
+        </is>
+      </c>
+      <c r="I53" s="27" t="inlineStr"/>
+    </row>
+    <row r="54">
+      <c r="A54" s="26" t="inlineStr"/>
+      <c r="B54" s="26" t="inlineStr">
+        <is>
+          <t>75 m³/h</t>
+        </is>
+      </c>
+      <c r="C54" s="25" t="n"/>
+      <c r="D54" s="26" t="inlineStr">
+        <is>
+          <t>14.8 Pa</t>
+        </is>
+      </c>
+      <c r="E54" s="25" t="n"/>
+      <c r="F54" s="26" t="inlineStr">
+        <is>
+          <t>8.8 Pa</t>
+        </is>
+      </c>
+      <c r="G54" s="25" t="n"/>
+      <c r="H54" s="26" t="inlineStr">
+        <is>
+          <t>+6.0 Pa</t>
+        </is>
+      </c>
+      <c r="I54" s="27" t="inlineStr"/>
+    </row>
+    <row r="55">
+      <c r="A55" s="26" t="inlineStr"/>
+      <c r="B55" s="26" t="inlineStr">
+        <is>
+          <t>80 m³/h</t>
+        </is>
+      </c>
+      <c r="C55" s="25" t="n"/>
+      <c r="D55" s="26" t="inlineStr">
+        <is>
+          <t>10.7 Pa</t>
+        </is>
+      </c>
+      <c r="E55" s="25" t="n"/>
+      <c r="F55" s="26" t="inlineStr">
+        <is>
+          <t>9.8 Pa</t>
+        </is>
+      </c>
+      <c r="G55" s="25" t="n"/>
+      <c r="H55" s="26" t="inlineStr">
+        <is>
+          <t>+0.8 Pa</t>
+        </is>
+      </c>
+      <c r="I55" s="27" t="inlineStr">
+        <is>
+          <t>← 有効換気量（交点・切捨て）</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="26" t="inlineStr"/>
+      <c r="B56" s="26" t="inlineStr">
+        <is>
+          <t>85 m³/h</t>
+        </is>
+      </c>
+      <c r="C56" s="25" t="n"/>
+      <c r="D56" s="26" t="inlineStr">
+        <is>
+          <t>5.2 Pa</t>
+        </is>
+      </c>
+      <c r="E56" s="25" t="n"/>
+      <c r="F56" s="26" t="inlineStr">
+        <is>
+          <t>10.9 Pa</t>
+        </is>
+      </c>
+      <c r="G56" s="25" t="n"/>
+      <c r="H56" s="26" t="inlineStr">
+        <is>
+          <t>-5.7 Pa</t>
+        </is>
+      </c>
+      <c r="I56" s="27" t="inlineStr"/>
+    </row>
+    <row r="57" ht="36" customHeight="1">
+      <c r="A57" s="18" t="inlineStr">
+        <is>
+          <t>※建設地（広島県三原市）は中国電力管内のため電源周波数60Hzで算定。参考：50Hzの場合 68 m³/h/台×3台＝204 m³/h（この場合も必要有効換気量以上）。開放風量（機外静圧0Pa）は50Hz 75／60Hz 90 m³/h、消費電力 4.3／5.0 W。</t>
+        </is>
+      </c>
+    </row>
+    <row r="58" ht="15" customHeight="1">
+      <c r="A58" s="18" t="inlineStr">
+        <is>
+          <t>※直管相当長を変更した場合は、P-Q線図で有効換気量（H列）を読み直すこと。</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="3" t="inlineStr">
         <is>
           <t>5. 判  定</t>
         </is>
       </c>
     </row>
-    <row r="52">
-      <c r="A52" s="4" t="inlineStr">
+    <row r="61">
+      <c r="A61" s="4" t="inlineStr">
         <is>
           <t>有効換気量 Ve</t>
         </is>
       </c>
-      <c r="B52" s="22" t="n"/>
-      <c r="C52" s="23" t="n"/>
-      <c r="D52" s="24">
+      <c r="B61" s="28" t="n"/>
+      <c r="C61" s="25" t="n"/>
+      <c r="D61" s="29">
         <f>H47</f>
         <v/>
       </c>
-      <c r="E52" s="23" t="n"/>
-      <c r="F52" s="25" t="inlineStr">
+      <c r="E61" s="25" t="n"/>
+      <c r="F61" s="30" t="inlineStr">
         <is>
           <t>≧</t>
         </is>
       </c>
-      <c r="G52" s="4" t="inlineStr">
+      <c r="G61" s="4" t="inlineStr">
         <is>
           <t>必要有効換気量 Vr</t>
         </is>
       </c>
-      <c r="H52" s="23" t="n"/>
-      <c r="I52" s="24">
+      <c r="H61" s="25" t="n"/>
+      <c r="I61" s="29">
         <f>H38</f>
         <v/>
       </c>
     </row>
-    <row r="53">
-      <c r="A53" s="26" t="inlineStr">
+    <row r="62">
+      <c r="A62" s="31" t="inlineStr">
         <is>
           <t>判定</t>
         </is>
       </c>
-      <c r="B53" s="22" t="n"/>
-      <c r="C53" s="23" t="n"/>
-      <c r="D53" s="27">
-        <f>IF(D52&gt;=I52,"適合（OK）","不適合（NG）")</f>
-        <v/>
-      </c>
-      <c r="E53" s="22" t="n"/>
-      <c r="F53" s="23" t="n"/>
-      <c r="G53" s="4" t="inlineStr">
+      <c r="B62" s="28" t="n"/>
+      <c r="C62" s="25" t="n"/>
+      <c r="D62" s="32">
+        <f>IF(D61&gt;=I61,"適合（OK）","不適合（NG）")</f>
+        <v/>
+      </c>
+      <c r="E62" s="28" t="n"/>
+      <c r="F62" s="25" t="n"/>
+      <c r="G62" s="4" t="inlineStr">
         <is>
           <t>余裕率 Ve/Vr</t>
         </is>
       </c>
-      <c r="H53" s="23" t="n"/>
-      <c r="I53" s="28">
-        <f>ROUND(D52/I52,2)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54" s="20" t="inlineStr">
+      <c r="H62" s="25" t="n"/>
+      <c r="I62" s="33">
+        <f>ROUND(D61/I61,2)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="21" t="inlineStr">
         <is>
           <t>参考：外陣・内陣・護摩堂の天井高が一律 H(m) のとき適合する上限</t>
         </is>
       </c>
-      <c r="H54" s="29">
-        <f>ROUNDDOWN((D52-(I52-(H22+H24+H25)))/(0.3*(D22+D24+D25)),2)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="56">
-      <c r="A56" s="3" t="inlineStr">
+      <c r="H63" s="34">
+        <f>ROUNDDOWN((D61-(I61-(H22+H24+H25)))/(0.3*(D22+D24+D25)),2)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="3" t="inlineStr">
         <is>
           <t>6. 給気口（外気導入）</t>
         </is>
       </c>
     </row>
-    <row r="57">
-      <c r="A57" s="30" t="inlineStr">
+    <row r="66">
+      <c r="A66" s="24" t="inlineStr">
         <is>
           <t>記号</t>
         </is>
       </c>
-      <c r="B57" s="30" t="inlineStr">
+      <c r="B66" s="24" t="inlineStr">
         <is>
           <t>設置室</t>
         </is>
       </c>
-      <c r="C57" s="30" t="inlineStr">
+      <c r="C66" s="24" t="inlineStr">
         <is>
           <t>台数</t>
         </is>
       </c>
-      <c r="D57" s="30" t="inlineStr">
+      <c r="D66" s="24" t="inlineStr">
         <is>
           <t>ダクト径</t>
         </is>
       </c>
-      <c r="E57" s="30" t="inlineStr">
+      <c r="E66" s="24" t="inlineStr">
         <is>
           <t>型式</t>
         </is>
       </c>
-      <c r="F57" s="22" t="n"/>
-      <c r="G57" s="22" t="n"/>
-      <c r="H57" s="23" t="n"/>
-      <c r="I57" s="30" t="inlineStr">
+      <c r="F66" s="28" t="n"/>
+      <c r="G66" s="28" t="n"/>
+      <c r="H66" s="25" t="n"/>
+      <c r="I66" s="24" t="inlineStr">
         <is>
           <t>仕様</t>
         </is>
       </c>
     </row>
-    <row r="58">
-      <c r="A58" s="10" t="inlineStr">
+    <row r="67">
+      <c r="A67" s="10" t="inlineStr">
         <is>
           <t>SA-1</t>
         </is>
       </c>
-      <c r="B58" s="11" t="inlineStr">
+      <c r="B67" s="11" t="inlineStr">
         <is>
           <t>外陣（大間）</t>
         </is>
       </c>
-      <c r="C58" s="10" t="n">
+      <c r="C67" s="10" t="n">
         <v>3</v>
       </c>
-      <c r="D58" s="10" t="inlineStr">
+      <c r="D67" s="10" t="inlineStr">
         <is>
           <t>φ200</t>
         </is>
       </c>
-      <c r="E58" s="11" t="inlineStr">
-        <is>
-          <t>パナソニック VB-GE200P-T</t>
-        </is>
-      </c>
-      <c r="F58" s="22" t="n"/>
-      <c r="G58" s="22" t="n"/>
-      <c r="H58" s="23" t="n"/>
-      <c r="I58" s="11" t="inlineStr">
-        <is>
-          <t>シャッター・フィルター付（ライトブラウン）</t>
-        </is>
-      </c>
-    </row>
-    <row r="59">
-      <c r="A59" s="10" t="inlineStr">
+      <c r="E67" s="11" t="inlineStr">
+        <is>
+          <t>三菱電機 P-23GHF5</t>
+        </is>
+      </c>
+      <c r="F67" s="28" t="n"/>
+      <c r="G67" s="28" t="n"/>
+      <c r="H67" s="25" t="n"/>
+      <c r="I67" s="11" t="inlineStr">
+        <is>
+          <t>ネットフィルター付</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="10" t="inlineStr">
         <is>
           <t>SA-1</t>
         </is>
       </c>
-      <c r="B59" s="11" t="inlineStr">
+      <c r="B68" s="11" t="inlineStr">
         <is>
           <t>内陣（本陣・御本尊）</t>
         </is>
       </c>
-      <c r="C59" s="10" t="n">
+      <c r="C68" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="D59" s="10" t="inlineStr">
+      <c r="D68" s="10" t="inlineStr">
         <is>
           <t>φ200</t>
         </is>
       </c>
-      <c r="E59" s="11" t="inlineStr">
-        <is>
-          <t>パナソニック VB-GE200P-T</t>
-        </is>
-      </c>
-      <c r="F59" s="22" t="n"/>
-      <c r="G59" s="22" t="n"/>
-      <c r="H59" s="23" t="n"/>
-      <c r="I59" s="11" t="inlineStr">
-        <is>
-          <t>シャッター・フィルター付（ライトブラウン）</t>
-        </is>
-      </c>
-    </row>
-    <row r="60">
-      <c r="A60" s="10" t="inlineStr">
+      <c r="E68" s="11" t="inlineStr">
+        <is>
+          <t>三菱電機 P-23GHF5</t>
+        </is>
+      </c>
+      <c r="F68" s="28" t="n"/>
+      <c r="G68" s="28" t="n"/>
+      <c r="H68" s="25" t="n"/>
+      <c r="I68" s="11" t="inlineStr">
+        <is>
+          <t>ネットフィルター付</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="10" t="inlineStr">
         <is>
           <t>SA-2</t>
         </is>
       </c>
-      <c r="B60" s="11" t="inlineStr">
+      <c r="B69" s="11" t="inlineStr">
         <is>
           <t>護摩堂</t>
         </is>
       </c>
-      <c r="C60" s="10" t="n">
+      <c r="C69" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="D60" s="10" t="inlineStr">
+      <c r="D69" s="10" t="inlineStr">
         <is>
           <t>φ150</t>
         </is>
       </c>
-      <c r="E60" s="11" t="inlineStr">
-        <is>
-          <t>パナソニック VB-GE150P-T</t>
-        </is>
-      </c>
-      <c r="F60" s="22" t="n"/>
-      <c r="G60" s="22" t="n"/>
-      <c r="H60" s="23" t="n"/>
-      <c r="I60" s="11" t="inlineStr">
-        <is>
-          <t>シャッター・フィルター付（ライトブラウン）</t>
-        </is>
-      </c>
-    </row>
-    <row r="61">
-      <c r="A61" s="10" t="inlineStr">
+      <c r="E69" s="11" t="inlineStr">
+        <is>
+          <t>三菱電機 P-18GHF5</t>
+        </is>
+      </c>
+      <c r="F69" s="28" t="n"/>
+      <c r="G69" s="28" t="n"/>
+      <c r="H69" s="25" t="n"/>
+      <c r="I69" s="11" t="inlineStr">
+        <is>
+          <t>ネットフィルター付</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="10" t="inlineStr">
         <is>
           <t>SA-3</t>
         </is>
       </c>
-      <c r="B61" s="11" t="inlineStr">
+      <c r="B70" s="11" t="inlineStr">
         <is>
           <t>和室(1)</t>
         </is>
       </c>
-      <c r="C61" s="10" t="n">
+      <c r="C70" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="D61" s="10" t="inlineStr">
+      <c r="D70" s="10" t="inlineStr">
         <is>
           <t>φ100</t>
         </is>
       </c>
-      <c r="E61" s="11" t="inlineStr">
-        <is>
-          <t>パナソニック VB-GE100P3-T</t>
-        </is>
-      </c>
-      <c r="F61" s="22" t="n"/>
-      <c r="G61" s="22" t="n"/>
-      <c r="H61" s="23" t="n"/>
-      <c r="I61" s="11" t="inlineStr">
-        <is>
-          <t>シャッター・フィルター付（ライトブラウン）</t>
-        </is>
-      </c>
-    </row>
-    <row r="62">
-      <c r="A62" s="10" t="inlineStr">
+      <c r="E70" s="11" t="inlineStr">
+        <is>
+          <t>三菱電機 P-13GHF5</t>
+        </is>
+      </c>
+      <c r="F70" s="28" t="n"/>
+      <c r="G70" s="28" t="n"/>
+      <c r="H70" s="25" t="n"/>
+      <c r="I70" s="11" t="inlineStr">
+        <is>
+          <t>ネットフィルター付</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="10" t="inlineStr">
         <is>
           <t>SA-3</t>
         </is>
       </c>
-      <c r="B62" s="11" t="inlineStr">
+      <c r="B71" s="11" t="inlineStr">
         <is>
           <t>和室(2)</t>
         </is>
       </c>
-      <c r="C62" s="10" t="n">
+      <c r="C71" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="D62" s="10" t="inlineStr">
+      <c r="D71" s="10" t="inlineStr">
         <is>
           <t>φ100</t>
         </is>
       </c>
-      <c r="E62" s="11" t="inlineStr">
-        <is>
-          <t>パナソニック VB-GE100P3-T</t>
-        </is>
-      </c>
-      <c r="F62" s="22" t="n"/>
-      <c r="G62" s="22" t="n"/>
-      <c r="H62" s="23" t="n"/>
-      <c r="I62" s="11" t="inlineStr">
-        <is>
-          <t>シャッター・フィルター付（ライトブラウン）</t>
-        </is>
-      </c>
-    </row>
-    <row r="63">
-      <c r="A63" s="10" t="inlineStr">
-        <is>
-          <t>SA-4</t>
-        </is>
-      </c>
-      <c r="B63" s="11" t="inlineStr">
+      <c r="E71" s="11" t="inlineStr">
+        <is>
+          <t>三菱電機 P-13GHF5</t>
+        </is>
+      </c>
+      <c r="F71" s="28" t="n"/>
+      <c r="G71" s="28" t="n"/>
+      <c r="H71" s="25" t="n"/>
+      <c r="I71" s="11" t="inlineStr">
+        <is>
+          <t>ネットフィルター付</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="10" t="inlineStr">
+        <is>
+          <t>SA-3</t>
+        </is>
+      </c>
+      <c r="B72" s="11" t="inlineStr">
         <is>
           <t>談話室</t>
         </is>
       </c>
-      <c r="C63" s="10" t="n">
+      <c r="C72" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="D63" s="10" t="inlineStr">
+      <c r="D72" s="10" t="inlineStr">
         <is>
           <t>φ100</t>
         </is>
       </c>
-      <c r="E63" s="11" t="inlineStr">
-        <is>
-          <t>パナソニック VB-GE100P3-W</t>
-        </is>
-      </c>
-      <c r="F63" s="22" t="n"/>
-      <c r="G63" s="22" t="n"/>
-      <c r="H63" s="23" t="n"/>
-      <c r="I63" s="11" t="inlineStr">
-        <is>
-          <t>シャッター・フィルター付（ホワイト）</t>
-        </is>
-      </c>
-    </row>
-    <row r="64" ht="24" customHeight="1">
-      <c r="A64" s="18" t="inlineStr">
+      <c r="E72" s="11" t="inlineStr">
+        <is>
+          <t>三菱電機 P-13GHF5</t>
+        </is>
+      </c>
+      <c r="F72" s="28" t="n"/>
+      <c r="G72" s="28" t="n"/>
+      <c r="H72" s="25" t="n"/>
+      <c r="I72" s="11" t="inlineStr">
+        <is>
+          <t>ネットフィルター付</t>
+        </is>
+      </c>
+    </row>
+    <row r="73" ht="24" customHeight="1">
+      <c r="A73" s="18" t="inlineStr">
         <is>
           <t>※給気口は居室の天井付近に設け、外壁貫通部に深型フード（防虫網付）を設けて外気流・雨水の逆流を防止する。</t>
-        </is>
-      </c>
-    </row>
-    <row r="66">
-      <c r="A66" s="3" t="inlineStr">
-        <is>
-          <t>7. 換気経路・その他の措置</t>
-        </is>
-      </c>
-    </row>
-    <row r="67" ht="27" customHeight="1">
-      <c r="A67" s="31" t="inlineStr">
-        <is>
-          <t>(1) 換気経路：給気口（各居室）→ 居室建具（アンダーカット）→ 廊下・ホール → 便所建具 → 排気機（EF-1）→ 屋外。</t>
-        </is>
-      </c>
-    </row>
-    <row r="68" ht="27" customHeight="1">
-      <c r="A68" s="31" t="inlineStr">
-        <is>
-          <t>(2) 建具：居室・廊下の建具はアンダーカット10mm以上（有効開口面積100cm²以上）、便所の建具はアンダーカット20mm以上又はガラリ。</t>
-        </is>
-      </c>
-    </row>
-    <row r="69" ht="27" customHeight="1">
-      <c r="A69" s="31" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    障子・襖・格子戸等で常時通気が確保されるものはこれによる。</t>
-        </is>
-      </c>
-    </row>
-    <row r="70" ht="27" customHeight="1">
-      <c r="A70" s="31" t="inlineStr">
-        <is>
-          <t>(3) 排気機（EF-1）は24時間常時運転とし、スイッチに「24時間換気（常時運転）」の表示を行う。</t>
-        </is>
-      </c>
-    </row>
-    <row r="71" ht="27" customHeight="1">
-      <c r="A71" s="31" t="inlineStr">
-        <is>
-          <t>(4) 内装仕上げの制限（令20条の7）：居室の内装仕上げには第1種・第2種ホルムアルデヒド発散建築材料を使用しない（F☆☆☆☆ 又は規制対象外の材料とする）。</t>
-        </is>
-      </c>
-    </row>
-    <row r="72" ht="27" customHeight="1">
-      <c r="A72" s="31" t="inlineStr">
-        <is>
-          <t>(5) 天井裏等の措置（令20条の9・平15国交告第274号）：天井裏・小屋裏・床下・壁内・収納の下地材等にF☆☆☆以上の建築材料を用いる（建材による措置）。※意匠仕様と整合のこと。</t>
-        </is>
-      </c>
-    </row>
-    <row r="73" ht="27" customHeight="1">
-      <c r="A73" s="31" t="inlineStr">
-        <is>
-          <t>(6) 換気設備の構造（令129条の2の5）：給気口・排気口は外気流によって換気能力が低下しない構造（深型フード）とし、防虫網を設ける。</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="3" t="inlineStr">
         <is>
+          <t>7. 換気経路・その他の措置</t>
+        </is>
+      </c>
+    </row>
+    <row r="76" ht="27" customHeight="1">
+      <c r="A76" s="23" t="inlineStr">
+        <is>
+          <t>(1) 換気経路：給気口（各居室）→ 居室建具（アンダーカット）→ 廊下・ホール → 便所建具 → 排気機（EF-1）→ 屋外。</t>
+        </is>
+      </c>
+    </row>
+    <row r="77" ht="27" customHeight="1">
+      <c r="A77" s="23" t="inlineStr">
+        <is>
+          <t>(2) 建具：居室・廊下の建具はアンダーカット10mm以上（有効開口面積100cm²以上）、便所の建具はアンダーカット20mm以上又はガラリ。</t>
+        </is>
+      </c>
+    </row>
+    <row r="78" ht="27" customHeight="1">
+      <c r="A78" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    障子・襖・格子戸等で常時通気が確保されるものはこれによる。</t>
+        </is>
+      </c>
+    </row>
+    <row r="79" ht="27" customHeight="1">
+      <c r="A79" s="23" t="inlineStr">
+        <is>
+          <t>(3) 排気機（EF-1 パイプ用ファン）は24時間常時運転とし、スイッチに「24時間換気（常時運転）」の表示を行う。</t>
+        </is>
+      </c>
+    </row>
+    <row r="80" ht="27" customHeight="1">
+      <c r="A80" s="23" t="inlineStr">
+        <is>
+          <t>(4) 内装仕上げの制限（令20条の7）：居室の内装仕上げには第1種・第2種ホルムアルデヒド発散建築材料を使用しない（F☆☆☆☆ 又は規制対象外の材料とする）。</t>
+        </is>
+      </c>
+    </row>
+    <row r="81" ht="27" customHeight="1">
+      <c r="A81" s="23" t="inlineStr">
+        <is>
+          <t>(5) 天井裏等の措置（令20条の9・平15国交告第274号）：天井裏・小屋裏・床下・壁内・収納の下地材等にF☆☆☆以上の建築材料を用いる（建材による措置）。※意匠仕様と整合のこと。</t>
+        </is>
+      </c>
+    </row>
+    <row r="82" ht="27" customHeight="1">
+      <c r="A82" s="23" t="inlineStr">
+        <is>
+          <t>(6) 換気設備の構造（令129条の2の5）：給気口・排気口は外気流によって換気能力が低下しない構造（深型フード）とし、防虫網を設ける。</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" s="3" t="inlineStr">
+        <is>
           <t>8. 前提条件・要確認事項</t>
         </is>
       </c>
     </row>
-    <row r="76" ht="27" customHeight="1">
-      <c r="A76" s="31" t="inlineStr">
+    <row r="85" ht="27" customHeight="1">
+      <c r="A85" s="23" t="inlineStr">
         <is>
           <t>・天井高（特に外陣・内陣・護摩堂の格天井・折上天井）は仮定値。矩計図・断面図確定後に本書を更新すること。</t>
         </is>
       </c>
     </row>
-    <row r="77" ht="27" customHeight="1">
-      <c r="A77" s="31" t="inlineStr">
-        <is>
-          <t>・機器配置・ダクトルートは設計段階の計画。施工図段階でダクト直管相当長が20mを超える場合はP-Q曲線で有効換気量を確認する。</t>
-        </is>
-      </c>
-    </row>
-    <row r="78" ht="27" customHeight="1">
-      <c r="A78" s="31" t="inlineStr">
-        <is>
-          <t>・換気機器はパナソニック「換気システムご提案書」（当初プラン）を基に、現行平面図（令和8年7月20日版）に合わせて配置を修正した。</t>
-        </is>
-      </c>
-    </row>
-    <row r="79" ht="27" customHeight="1">
-      <c r="A79" s="31" t="inlineStr">
-        <is>
-          <t>・電源（EF-1 単相100V 常時通電回路）は電気設備工事による。</t>
+    <row r="86" ht="27" customHeight="1">
+      <c r="A86" s="23" t="inlineStr">
+        <is>
+          <t>・機器配置・ダクトルートは設計段階の計画。施工図段階で排気側の直管相当長が変わる場合はP-Q線図で有効換気量を確認する。</t>
+        </is>
+      </c>
+    </row>
+    <row r="87" ht="27" customHeight="1">
+      <c r="A87" s="23" t="inlineStr">
+        <is>
+          <t>・換気機器は三菱電機製とする（パナソニック当初提案から変更）。性能値は三菱電機の納入仕様書・P-Q線図による。</t>
+        </is>
+      </c>
+    </row>
+    <row r="88" ht="27" customHeight="1">
+      <c r="A88" s="23" t="inlineStr">
+        <is>
+          <t>・電源（EF-1 単相100V 常時通電回路、スイッチは常時運転表示付）は電気設備工事による。</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="61">
+  <mergeCells count="81">
+    <mergeCell ref="A2:I2"/>
+    <mergeCell ref="A85:I85"/>
+    <mergeCell ref="A42:I42"/>
+    <mergeCell ref="A17:I17"/>
+    <mergeCell ref="D61:E61"/>
+    <mergeCell ref="E71:H71"/>
+    <mergeCell ref="D48:E48"/>
+    <mergeCell ref="D5:I5"/>
+    <mergeCell ref="A39:I39"/>
+    <mergeCell ref="D56:E56"/>
+    <mergeCell ref="F56:G56"/>
+    <mergeCell ref="B55:C55"/>
+    <mergeCell ref="B51:C51"/>
+    <mergeCell ref="A6:C6"/>
+    <mergeCell ref="D51:E51"/>
+    <mergeCell ref="A79:I79"/>
+    <mergeCell ref="D6:I6"/>
+    <mergeCell ref="A87:I87"/>
+    <mergeCell ref="A48:B48"/>
+    <mergeCell ref="F54:G54"/>
+    <mergeCell ref="G61:H61"/>
+    <mergeCell ref="A63:G63"/>
+    <mergeCell ref="D7:I7"/>
+    <mergeCell ref="A5:C5"/>
+    <mergeCell ref="A76:I76"/>
+    <mergeCell ref="G62:H62"/>
+    <mergeCell ref="E67:H67"/>
+    <mergeCell ref="B53:C53"/>
+    <mergeCell ref="D8:I8"/>
+    <mergeCell ref="D53:E53"/>
+    <mergeCell ref="A77:I77"/>
+    <mergeCell ref="A1:I1"/>
+    <mergeCell ref="A7:C7"/>
+    <mergeCell ref="A78:I78"/>
     <mergeCell ref="D11:I11"/>
-    <mergeCell ref="A48:B48"/>
-    <mergeCell ref="G52:H52"/>
-    <mergeCell ref="E61:H61"/>
+    <mergeCell ref="A65:I65"/>
+    <mergeCell ref="B54:C54"/>
     <mergeCell ref="A75:I75"/>
-    <mergeCell ref="E57:H57"/>
-    <mergeCell ref="A66:I66"/>
+    <mergeCell ref="A80:I80"/>
+    <mergeCell ref="B56:C56"/>
+    <mergeCell ref="E66:H66"/>
+    <mergeCell ref="B52:C52"/>
+    <mergeCell ref="A57:I57"/>
+    <mergeCell ref="D52:E52"/>
+    <mergeCell ref="A14:I14"/>
+    <mergeCell ref="D9:I9"/>
+    <mergeCell ref="A62:C62"/>
+    <mergeCell ref="E68:H68"/>
+    <mergeCell ref="A4:I4"/>
+    <mergeCell ref="A40:I40"/>
+    <mergeCell ref="A82:I82"/>
+    <mergeCell ref="D10:I10"/>
+    <mergeCell ref="D55:E55"/>
+    <mergeCell ref="A61:C61"/>
+    <mergeCell ref="D54:E54"/>
+    <mergeCell ref="A16:I16"/>
+    <mergeCell ref="E70:H70"/>
+    <mergeCell ref="A84:I84"/>
     <mergeCell ref="A18:I18"/>
-    <mergeCell ref="A56:I56"/>
-    <mergeCell ref="D53:F53"/>
-    <mergeCell ref="D7:I7"/>
-    <mergeCell ref="A2:I2"/>
-    <mergeCell ref="D52:E52"/>
-    <mergeCell ref="A71:I71"/>
-    <mergeCell ref="A5:C5"/>
-    <mergeCell ref="A42:I42"/>
-    <mergeCell ref="A76:I76"/>
+    <mergeCell ref="E72:H72"/>
+    <mergeCell ref="A50:I50"/>
+    <mergeCell ref="A86:I86"/>
+    <mergeCell ref="F55:G55"/>
     <mergeCell ref="A8:C8"/>
-    <mergeCell ref="A14:I14"/>
-    <mergeCell ref="E58:H58"/>
-    <mergeCell ref="D9:I9"/>
-    <mergeCell ref="A17:I17"/>
-    <mergeCell ref="G53:H53"/>
-    <mergeCell ref="E62:H62"/>
-    <mergeCell ref="A53:C53"/>
-    <mergeCell ref="D48:E48"/>
-    <mergeCell ref="A4:I4"/>
+    <mergeCell ref="F51:G51"/>
+    <mergeCell ref="D62:F62"/>
     <mergeCell ref="A20:I20"/>
-    <mergeCell ref="D8:I8"/>
-    <mergeCell ref="A52:C52"/>
     <mergeCell ref="A10:C10"/>
-    <mergeCell ref="A72:I72"/>
-    <mergeCell ref="A68:I68"/>
-    <mergeCell ref="D5:I5"/>
+    <mergeCell ref="A81:I81"/>
     <mergeCell ref="A13:I13"/>
     <mergeCell ref="A9:C9"/>
-    <mergeCell ref="A40:I40"/>
-    <mergeCell ref="A54:G54"/>
-    <mergeCell ref="A67:I67"/>
-    <mergeCell ref="A39:I39"/>
-    <mergeCell ref="A77:I77"/>
-    <mergeCell ref="E63:H63"/>
+    <mergeCell ref="A58:I58"/>
+    <mergeCell ref="F52:G52"/>
     <mergeCell ref="A15:I15"/>
-    <mergeCell ref="A64:I64"/>
-    <mergeCell ref="D10:I10"/>
-    <mergeCell ref="E60:H60"/>
+    <mergeCell ref="A73:I73"/>
     <mergeCell ref="A11:C11"/>
-    <mergeCell ref="A49:I49"/>
-    <mergeCell ref="A51:I51"/>
-    <mergeCell ref="A73:I73"/>
-    <mergeCell ref="A6:C6"/>
-    <mergeCell ref="A1:I1"/>
-    <mergeCell ref="A70:I70"/>
-    <mergeCell ref="A79:I79"/>
+    <mergeCell ref="E69:H69"/>
+    <mergeCell ref="A60:I60"/>
+    <mergeCell ref="A88:I88"/>
     <mergeCell ref="G48:I48"/>
-    <mergeCell ref="E59:H59"/>
-    <mergeCell ref="D6:I6"/>
-    <mergeCell ref="A69:I69"/>
-    <mergeCell ref="A7:C7"/>
-    <mergeCell ref="A78:I78"/>
-    <mergeCell ref="A16:I16"/>
+    <mergeCell ref="F53:G53"/>
   </mergeCells>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.5" right="0.4" top="0.6" bottom="0.6" header="0.5" footer="0.5"/>
@@ -2174,7 +2380,7 @@
     <firstFooter/>
   </headerFooter>
   <rowBreaks count="1" manualBreakCount="1">
-    <brk id="65" min="0" max="16383" man="1"/>
+    <brk id="74" min="0" max="16383" man="1"/>
   </rowBreaks>
 </worksheet>
 </file>